--- a/output/tables/universal_sm_hybrid/hybrid_by_route.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_by_route.xlsx
@@ -389,19 +389,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>1914</v>
+        <v>1828</v>
       </c>
       <c r="C2" t="n">
-        <v>19.4146300552779</v>
+        <v>18.4891458945881</v>
       </c>
       <c r="D2" t="n">
-        <v>42436.6793019121</v>
+        <v>41301.1279882902</v>
       </c>
       <c r="E2" t="n">
-        <v>65.2398184760953</v>
+        <v>65.7772203210134</v>
       </c>
       <c r="F2" t="n">
-        <v>10452.1104090432</v>
+        <v>9916.42468871174</v>
       </c>
     </row>
     <row r="3">
@@ -409,19 +409,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>2813</v>
+        <v>2743</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6521032626311</v>
+        <v>25.9833265074087</v>
       </c>
       <c r="D3" t="n">
-        <v>35452.3328727742</v>
+        <v>34767.7775508686</v>
       </c>
       <c r="E3" t="n">
-        <v>84.8234824192668</v>
+        <v>84.7042163740556</v>
       </c>
       <c r="F3" t="n">
-        <v>14470.4163753296</v>
+        <v>13949.1949654053</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/universal_sm_hybrid/hybrid_by_route.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_by_route.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">route_chr</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">full_participation_cost_M_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed_cost_M_num</t>
   </si>
   <si>
     <t xml:space="preserve">employer_plan</t>
@@ -383,10 +386,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
         <v>1828</v>
@@ -402,11 +408,14 @@
       </c>
       <c r="F2" t="n">
         <v>9916.42468871174</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1848.91458945881</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
         <v>2743</v>
@@ -422,6 +431,9 @@
       </c>
       <c r="F3" t="n">
         <v>13949.1949654053</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2598.33265074087</v>
       </c>
     </row>
   </sheetData>
